--- a/research/traditional_assets/database/data/tunisia/tunisia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0319</v>
+        <v>0.0413</v>
       </c>
       <c r="E2">
-        <v>0.0351</v>
+        <v>0.0303</v>
       </c>
       <c r="G2">
-        <v>0.9423592493297588</v>
+        <v>0.9221476510067114</v>
       </c>
       <c r="H2">
-        <v>0.9423592493297588</v>
+        <v>0.9221476510067114</v>
       </c>
       <c r="I2">
-        <v>0.9664879356568364</v>
+        <v>0.9704697986577182</v>
       </c>
       <c r="J2">
-        <v>0.9274941860914309</v>
+        <v>0.9262152374579307</v>
       </c>
       <c r="K2">
-        <v>6.66</v>
+        <v>6.51</v>
       </c>
       <c r="L2">
-        <v>0.8927613941018767</v>
+        <v>0.8738255033557046</v>
       </c>
       <c r="M2">
-        <v>6.05</v>
+        <v>5.44</v>
       </c>
       <c r="N2">
-        <v>0.07333333333333333</v>
+        <v>0.07941605839416059</v>
       </c>
       <c r="O2">
-        <v>0.9084084084084083</v>
+        <v>0.8356374807987712</v>
       </c>
       <c r="P2">
-        <v>6.05</v>
+        <v>5.44</v>
       </c>
       <c r="Q2">
-        <v>0.07333333333333333</v>
+        <v>0.07941605839416059</v>
       </c>
       <c r="R2">
-        <v>0.9084084084084083</v>
+        <v>0.8356374807987712</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.104</v>
+        <v>13.4</v>
       </c>
       <c r="V2">
-        <v>0.001260606060606061</v>
+        <v>0.1956204379562044</v>
       </c>
       <c r="W2">
-        <v>0.2729508196721312</v>
+        <v>0.2523255813953488</v>
       </c>
       <c r="X2">
-        <v>0.09720280188600179</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="Y2">
-        <v>0.1757480177861294</v>
+        <v>0.1062245874413353</v>
       </c>
       <c r="Z2">
-        <v>0.3101871101871102</v>
+        <v>0.2899283935242839</v>
       </c>
       <c r="AA2">
-        <v>0.2876967412990468</v>
+        <v>0.268536095853891</v>
       </c>
       <c r="AB2">
-        <v>0.09720280188600179</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="AC2">
-        <v>0.190493939413045</v>
+        <v>0.1224351018998775</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.104</v>
+        <v>-13.4</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.001262197194038545</v>
+        <v>-0.2431941923774955</v>
       </c>
       <c r="AK2">
-        <v>-0.004047322540473225</v>
+        <v>-1.240740740740741</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.01438450899031812</v>
+        <v>-1.900709219858156</v>
       </c>
       <c r="AQ2">
-        <v>-2403.333333333333</v>
+        <v>-1446</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0319</v>
+        <v>0.0413</v>
       </c>
       <c r="E3">
-        <v>0.0351</v>
+        <v>0.0303</v>
       </c>
       <c r="G3">
-        <v>0.9423592493297588</v>
+        <v>0.9221476510067114</v>
       </c>
       <c r="H3">
-        <v>0.9423592493297588</v>
+        <v>0.9221476510067114</v>
       </c>
       <c r="I3">
-        <v>0.9664879356568364</v>
+        <v>0.9704697986577182</v>
       </c>
       <c r="J3">
-        <v>0.9274941860914309</v>
+        <v>0.9262152374579307</v>
       </c>
       <c r="K3">
-        <v>6.66</v>
+        <v>6.51</v>
       </c>
       <c r="L3">
-        <v>0.8927613941018767</v>
+        <v>0.8738255033557046</v>
       </c>
       <c r="M3">
-        <v>6.05</v>
+        <v>5.44</v>
       </c>
       <c r="N3">
-        <v>0.07333333333333333</v>
+        <v>0.07941605839416059</v>
       </c>
       <c r="O3">
-        <v>0.9084084084084083</v>
+        <v>0.8356374807987712</v>
       </c>
       <c r="P3">
-        <v>6.05</v>
+        <v>5.44</v>
       </c>
       <c r="Q3">
-        <v>0.07333333333333333</v>
+        <v>0.07941605839416059</v>
       </c>
       <c r="R3">
-        <v>0.9084084084084083</v>
+        <v>0.8356374807987712</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.104</v>
+        <v>13.4</v>
       </c>
       <c r="V3">
-        <v>0.001260606060606061</v>
+        <v>0.1956204379562044</v>
       </c>
       <c r="W3">
-        <v>0.2729508196721312</v>
+        <v>0.2523255813953488</v>
       </c>
       <c r="X3">
-        <v>0.09720280188600179</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="Y3">
-        <v>0.1757480177861294</v>
+        <v>0.1062245874413353</v>
       </c>
       <c r="Z3">
-        <v>0.3101871101871102</v>
+        <v>0.2899283935242839</v>
       </c>
       <c r="AA3">
-        <v>0.2876967412990468</v>
+        <v>0.268536095853891</v>
       </c>
       <c r="AB3">
-        <v>0.09720280188600179</v>
+        <v>0.1461009939540135</v>
       </c>
       <c r="AC3">
-        <v>0.190493939413045</v>
+        <v>0.1224351018998775</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.104</v>
+        <v>-13.4</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.001262197194038545</v>
+        <v>-0.2431941923774955</v>
       </c>
       <c r="AK3">
-        <v>-0.004047322540473225</v>
+        <v>-1.240740740740741</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.01438450899031812</v>
+        <v>-1.900709219858156</v>
       </c>
       <c r="AQ3">
-        <v>-2403.333333333333</v>
+        <v>-1446</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/tunisia/tunisia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_investments_asset_management.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0413</v>
+        <v>0.00363</v>
       </c>
       <c r="E2">
-        <v>0.0303</v>
+        <v>-0.00183</v>
       </c>
       <c r="G2">
-        <v>0.9221476510067114</v>
+        <v>0.9077490774907748</v>
       </c>
       <c r="H2">
-        <v>0.9221476510067114</v>
+        <v>0.9077490774907748</v>
       </c>
       <c r="I2">
-        <v>0.9704697986577182</v>
+        <v>0.9704797047970478</v>
       </c>
       <c r="J2">
-        <v>0.9262152374579307</v>
+        <v>0.9332013550609256</v>
       </c>
       <c r="K2">
-        <v>6.51</v>
+        <v>7.51</v>
       </c>
       <c r="L2">
-        <v>0.8738255033557046</v>
+        <v>0.9237392373923738</v>
       </c>
       <c r="M2">
-        <v>5.44</v>
+        <v>6.34</v>
       </c>
       <c r="N2">
-        <v>0.07941605839416059</v>
+        <v>0.08170103092783505</v>
       </c>
       <c r="O2">
-        <v>0.8356374807987712</v>
+        <v>0.844207723035952</v>
       </c>
       <c r="P2">
-        <v>5.44</v>
+        <v>6.34</v>
       </c>
       <c r="Q2">
-        <v>0.07941605839416059</v>
+        <v>0.08170103092783505</v>
       </c>
       <c r="R2">
-        <v>0.8356374807987712</v>
+        <v>0.844207723035952</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.4</v>
+        <v>11.3</v>
       </c>
       <c r="V2">
-        <v>0.1956204379562044</v>
+        <v>0.1456185567010309</v>
       </c>
       <c r="W2">
-        <v>0.2523255813953488</v>
+        <v>0.3103305785123967</v>
       </c>
       <c r="X2">
-        <v>0.1461009939540135</v>
+        <v>0.1295983166140643</v>
       </c>
       <c r="Y2">
-        <v>0.1062245874413353</v>
+        <v>0.1807322618983324</v>
       </c>
       <c r="Z2">
-        <v>0.2899283935242839</v>
+        <v>0.7527777777777779</v>
       </c>
       <c r="AA2">
-        <v>0.268536095853891</v>
+        <v>0.7024932422819747</v>
       </c>
       <c r="AB2">
-        <v>0.1461009939540135</v>
+        <v>0.1295983166140643</v>
       </c>
       <c r="AC2">
-        <v>0.1224351018998775</v>
+        <v>0.5728949256679103</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-13.4</v>
+        <v>-11.3</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2431941923774955</v>
+        <v>-0.1704374057315234</v>
       </c>
       <c r="AK2">
-        <v>-1.240740740740741</v>
+        <v>-0.8071428571428572</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.900709219858156</v>
+        <v>-1.430379746835443</v>
       </c>
       <c r="AQ2">
-        <v>-1446</v>
+        <v>-3945</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Societe de Placement et de Developpement Industriel et Touristique (BVMT:SPDIT)</t>
+          <t>Société de Placement &amp; de Développement Industriel &amp; Touristique Société anonyme (BVMT:SPDIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0413</v>
+        <v>0.00363</v>
       </c>
       <c r="E3">
-        <v>0.0303</v>
+        <v>-0.00183</v>
       </c>
       <c r="G3">
-        <v>0.9221476510067114</v>
+        <v>0.9077490774907748</v>
       </c>
       <c r="H3">
-        <v>0.9221476510067114</v>
+        <v>0.9077490774907748</v>
       </c>
       <c r="I3">
-        <v>0.9704697986577182</v>
+        <v>0.9704797047970478</v>
       </c>
       <c r="J3">
-        <v>0.9262152374579307</v>
+        <v>0.9332013550609256</v>
       </c>
       <c r="K3">
-        <v>6.51</v>
+        <v>7.51</v>
       </c>
       <c r="L3">
-        <v>0.8738255033557046</v>
+        <v>0.9237392373923738</v>
       </c>
       <c r="M3">
-        <v>5.44</v>
+        <v>6.34</v>
       </c>
       <c r="N3">
-        <v>0.07941605839416059</v>
+        <v>0.08170103092783505</v>
       </c>
       <c r="O3">
-        <v>0.8356374807987712</v>
+        <v>0.844207723035952</v>
       </c>
       <c r="P3">
-        <v>5.44</v>
+        <v>6.34</v>
       </c>
       <c r="Q3">
-        <v>0.07941605839416059</v>
+        <v>0.08170103092783505</v>
       </c>
       <c r="R3">
-        <v>0.8356374807987712</v>
+        <v>0.844207723035952</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>13.4</v>
+        <v>11.3</v>
       </c>
       <c r="V3">
-        <v>0.1956204379562044</v>
+        <v>0.1456185567010309</v>
       </c>
       <c r="W3">
-        <v>0.2523255813953488</v>
+        <v>0.3103305785123967</v>
       </c>
       <c r="X3">
-        <v>0.1461009939540135</v>
+        <v>0.1295983166140643</v>
       </c>
       <c r="Y3">
-        <v>0.1062245874413353</v>
+        <v>0.1807322618983324</v>
       </c>
       <c r="Z3">
-        <v>0.2899283935242839</v>
+        <v>0.7527777777777779</v>
       </c>
       <c r="AA3">
-        <v>0.268536095853891</v>
+        <v>0.7024932422819747</v>
       </c>
       <c r="AB3">
-        <v>0.1461009939540135</v>
+        <v>0.1295983166140643</v>
       </c>
       <c r="AC3">
-        <v>0.1224351018998775</v>
+        <v>0.5728949256679103</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-13.4</v>
+        <v>-11.3</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2431941923774955</v>
+        <v>-0.1704374057315234</v>
       </c>
       <c r="AK3">
-        <v>-1.240740740740741</v>
+        <v>-0.8071428571428572</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.900709219858156</v>
+        <v>-1.430379746835443</v>
       </c>
       <c r="AQ3">
-        <v>-1446</v>
+        <v>-3945</v>
       </c>
     </row>
   </sheetData>
